--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -39702,6 +39702,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1711">
+      <c r="A1711" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1711" t="n">
+        <v>5600</v>
+      </c>
+      <c r="C1711" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="D1711" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="E1711" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="F1711" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="G1711" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -39725,6 +39725,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1712">
+      <c r="A1712" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1712" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C1712" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="D1712" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="E1712" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="F1712" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="G1712" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -39748,6 +39748,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1713">
+      <c r="A1713" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1713" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1713" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="D1713" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="E1713" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="F1713" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="G1713" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1714" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1714" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="D1714" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="E1714" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="F1714" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="G1714" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -39612,7 +39612,7 @@
     </row>
     <row r="1707">
       <c r="A1707" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1707" t="n">
         <v>0</v>
@@ -39635,22 +39635,22 @@
     </row>
     <row r="1708">
       <c r="A1708" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1708" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="C1708" t="n">
         <v>1.5900000333786</v>
       </c>
       <c r="D1708" t="n">
-        <v>1.53999996185303</v>
+        <v>1.5900000333786</v>
       </c>
       <c r="E1708" t="n">
-        <v>1.53999996185303</v>
+        <v>1.5900000333786</v>
       </c>
       <c r="F1708" t="n">
-        <v>1.53999996185303</v>
+        <v>1.5900000333786</v>
       </c>
       <c r="G1708" t="s">
         <v>7</v>
@@ -39658,13 +39658,13 @@
     </row>
     <row r="1709">
       <c r="A1709" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1709" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="C1709" t="n">
-        <v>1.53999996185303</v>
+        <v>1.5900000333786</v>
       </c>
       <c r="D1709" t="n">
         <v>1.53999996185303</v>
@@ -39681,22 +39681,22 @@
     </row>
     <row r="1710">
       <c r="A1710" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1710" t="n">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="C1710" t="n">
-        <v>1.52999997138977</v>
+        <v>1.53999996185303</v>
       </c>
       <c r="D1710" t="n">
-        <v>1.48000001907349</v>
+        <v>1.53999996185303</v>
       </c>
       <c r="E1710" t="n">
-        <v>1.51999998092651</v>
+        <v>1.53999996185303</v>
       </c>
       <c r="F1710" t="n">
-        <v>1.52999997138977</v>
+        <v>1.53999996185303</v>
       </c>
       <c r="G1710" t="s">
         <v>7</v>
@@ -39704,22 +39704,22 @@
     </row>
     <row r="1711">
       <c r="A1711" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1711" t="n">
-        <v>5600</v>
+        <v>6400</v>
       </c>
       <c r="C1711" t="n">
-        <v>1.54999995231628</v>
+        <v>1.52999997138977</v>
       </c>
       <c r="D1711" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="E1711" t="n">
         <v>1.51999998092651</v>
       </c>
-      <c r="E1711" t="n">
+      <c r="F1711" t="n">
         <v>1.52999997138977</v>
-      </c>
-      <c r="F1711" t="n">
-        <v>1.54999995231628</v>
       </c>
       <c r="G1711" t="s">
         <v>7</v>
@@ -39727,22 +39727,22 @@
     </row>
     <row r="1712">
       <c r="A1712" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1712" t="n">
-        <v>2400</v>
+        <v>5600</v>
       </c>
       <c r="C1712" t="n">
-        <v>1.50999999046326</v>
+        <v>1.54999995231628</v>
       </c>
       <c r="D1712" t="n">
-        <v>1.50999999046326</v>
+        <v>1.51999998092651</v>
       </c>
       <c r="E1712" t="n">
-        <v>1.50999999046326</v>
+        <v>1.52999997138977</v>
       </c>
       <c r="F1712" t="n">
-        <v>1.50999999046326</v>
+        <v>1.54999995231628</v>
       </c>
       <c r="G1712" t="s">
         <v>7</v>
@@ -39750,10 +39750,10 @@
     </row>
     <row r="1713">
       <c r="A1713" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1713" t="n">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="C1713" t="n">
         <v>1.50999999046326</v>
@@ -39773,24 +39773,47 @@
     </row>
     <row r="1714">
       <c r="A1714" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1714" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="C1714" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="D1714" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="E1714" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="F1714" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="G1714" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1715" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C1715" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D1715" t="n">
         <v>1.58000004291534</v>
       </c>
-      <c r="D1714" t="n">
-        <v>1.51999998092651</v>
-      </c>
-      <c r="E1714" t="n">
-        <v>1.51999998092651</v>
-      </c>
-      <c r="F1714" t="n">
+      <c r="E1715" t="n">
         <v>1.58000004291534</v>
       </c>
-      <c r="G1714" t="s">
+      <c r="F1715" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="G1715" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -45017,6 +45017,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1718">
+      <c r="A1718" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1718" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C1718" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="D1718" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="E1718" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="F1718" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="G1718" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="H1718" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -45043,6 +45043,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1719">
+      <c r="A1719" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1719" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1719" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="D1719" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="E1719" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="F1719" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="G1719" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="H1719" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -39971,7 +39971,9 @@
       <c r="E1722" t="n">
         <v>1.60000002384186</v>
       </c>
-      <c r="F1722"/>
+      <c r="F1722" t="n">
+        <v>1.60000002384186</v>
+      </c>
       <c r="G1722" t="s">
         <v>7</v>
       </c>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -39978,6 +39978,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1723">
+      <c r="A1723" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B1723" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1723" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D1723" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="E1723" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="F1723" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="G1723" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -40001,6 +40001,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1724">
+      <c r="A1724" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1724" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1724" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D1724" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="E1724" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="F1724" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="G1724" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B1725" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1725" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="D1725" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="E1725" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="F1725"/>
+      <c r="G1725" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -40040,7 +40040,9 @@
       <c r="E1725" t="n">
         <v>1.55999994277954</v>
       </c>
-      <c r="F1725"/>
+      <c r="F1725" t="n">
+        <v>1.55999994277954</v>
+      </c>
       <c r="G1725" t="s">
         <v>7</v>
       </c>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -40047,6 +40047,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1726">
+      <c r="A1726" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1726" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1726" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="D1726" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="E1726" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="F1726" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="G1726" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1727" t="n">
+        <v>7600</v>
+      </c>
+      <c r="C1727" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="D1727" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E1727" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="F1727"/>
+      <c r="G1727" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -40086,8 +40086,31 @@
       <c r="E1727" t="n">
         <v>1.52999997138977</v>
       </c>
-      <c r="F1727"/>
+      <c r="F1727" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G1727" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1728" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1728" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="D1728" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="E1728" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="F1728"/>
+      <c r="G1728" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -40109,7 +40109,9 @@
       <c r="E1728" t="n">
         <v>1.48000001907349</v>
       </c>
-      <c r="F1728"/>
+      <c r="F1728" t="n">
+        <v>1.51999998092651</v>
+      </c>
       <c r="G1728" t="s">
         <v>7</v>
       </c>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -40116,6 +40116,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1729">
+      <c r="A1729" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1729" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1729" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="D1729" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="E1729" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="F1729" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="G1729" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1730" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C1730" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D1730" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="E1730" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="F1730"/>
+      <c r="G1730" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -40155,8 +40155,31 @@
       <c r="E1730" t="n">
         <v>1.46000003814697</v>
       </c>
-      <c r="F1730"/>
+      <c r="F1730" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G1730" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1731" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1731" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D1731" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="E1731" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F1731"/>
+      <c r="G1731" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -40185,6 +40185,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1732">
+      <c r="A1732" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1732" t="n">
+        <v>400</v>
+      </c>
+      <c r="C1732" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D1732" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E1732" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F1732" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G1732" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -40208,6 +40208,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1733">
+      <c r="A1733" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1733" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1733" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D1733" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E1733" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F1733" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G1733" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -40231,6 +40231,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1734">
+      <c r="A1734" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B1734" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1734" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D1734" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E1734" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F1734" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G1734" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -50722,6 +50722,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1737">
+      <c r="A1737" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1737" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1737" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="D1737" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="E1737" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="F1737" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="G1737" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="H1737" t="n">
+        <v>800</v>
+      </c>
+      <c r="I1737" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1738" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1738" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="D1738" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="E1738" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="F1738" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="G1738" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="H1738" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1738" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -50780,6 +50780,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1739">
+      <c r="A1739" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1739" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1739" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D1739" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E1739" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F1739" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G1739" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H1739" t="n">
+        <v>400</v>
+      </c>
+      <c r="I1739" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -50809,6 +50809,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1740">
+      <c r="A1740" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1740" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1740" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D1740" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E1740" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F1740" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G1740" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H1740" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1740" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1741" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1741" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="D1741" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="E1741" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="F1741" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="G1741" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="H1741" t="n">
+        <v>11600</v>
+      </c>
+      <c r="I1741" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -50867,6 +50867,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1742">
+      <c r="A1742" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1742" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1742" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="D1742" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="E1742" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F1742" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="G1742" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="H1742" t="n">
+        <v>4400</v>
+      </c>
+      <c r="I1742" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -50896,6 +50896,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1743">
+      <c r="A1743" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1743" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1743" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="D1743" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="E1743" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="F1743" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="G1743" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="H1743" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1743" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GIS.MI.xlsx
+++ b/data/GIS.MI.xlsx
@@ -50925,6 +50925,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1744">
+      <c r="A1744" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1744" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1744" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="D1744" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="E1744" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="F1744" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="G1744" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="H1744" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1745" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1745" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="D1745" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="E1745" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="F1745" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="G1745" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="H1745" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I1745" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
